--- a/intake_forms/025_faith_based_counseling_session_consent_form--intake_forms.xlsx
+++ b/intake_forms/025_faith_based_counseling_session_consent_form--intake_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -941,8 +941,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'once',_'value':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Once', 'value': 'once'}</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
@@ -1021,12 +1021,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'weekly',_'value':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly', 'value': 'weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1038,12 +1038,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'bi-weekly',_'value':_'biweekly'}</t>
+          <t>bi-weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Bi-Weekly', 'value': 'biweekly'}</t>
+          <t>Bi-Weekly</t>
         </is>
       </c>
     </row>
@@ -1055,12 +1055,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'monthly',_'value':_'monthly'}</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Monthly', 'value': 'monthly'}</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
